--- a/yanfeng/PKR确认信息/PKR完成情况（近两周）.xlsx
+++ b/yanfeng/PKR确认信息/PKR完成情况（近两周）.xlsx
@@ -590,7 +590,7 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Lu.Gongchao@yanfeng.com,Tao.Qichen@yanfeng.com,Wang23.Hao@yanfeng.com,Xu.Shirong@yanfeng.com,Zhao.Kailiang@yanfeng.com</t>
+          <t>Tao.Qichen@yanfeng.com,Wang23.Hao@yanfeng.com,Zhao.Kailiang@yanfeng.com</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
           <t>Total,0
 Wang Hao23,0
 Lu Dinghao,100
-Xu Shirong,0
+Xu Shirong,100
 Zhao Kailiang,0</t>
         </is>
       </c>
@@ -665,7 +665,6 @@
         <is>
           <t>Total,0
 Wang Hao23,0
-Xu Shirong,0
 Zhao Kailiang,0</t>
         </is>
       </c>
@@ -679,7 +678,7 @@
           <t>Total,Submitted
 Wang Hao23,style="color:
 Lu Dinghao,Submitted
-Xu Shirong,style="color:
+Xu Shirong,Submitted
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
@@ -826,16 +825,14 @@
           <t>Total,0
 Wang Hao23,0
 Lu Dinghao,100
-Lu Gongchao,0
-Xu Shirong,0</t>
+Lu Gongchao,100
+Xu Shirong,100</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>Total,0
-Wang Hao23,0
-Lu Gongchao,0
-Xu Shirong,0</t>
+Wang Hao23,0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -848,8 +845,8 @@
           <t>Total,Submitted
 Wang Hao23,style="color:
 Lu Dinghao,Submitted
-Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
+Lu Gongchao,Submitted
+Xu Shirong,Submitted</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -922,16 +919,14 @@
           <t>Total,0
 Wang Hao23,0
 Lu Dinghao,100
-Lu Gongchao,0
-Xu Shirong,0</t>
+Lu Gongchao,100
+Xu Shirong,100</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>Total,0
-Wang Hao23,0
-Lu Gongchao,0
-Xu Shirong,0</t>
+Wang Hao23,0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -944,8 +939,8 @@
           <t>Total,Submitted
 Wang Hao23,style="color:
 Lu Dinghao,Submitted
-Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
+Lu Gongchao,Submitted
+Xu Shirong,Submitted</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1458,7 +1453,7 @@
 Tao Qichen,0
 Wang Hao23,100
 Lu Dinghao,100
-Xu Shirong,0
+Xu Shirong,100
 Zhao Kailiang,0</t>
         </is>
       </c>
@@ -1466,7 +1461,6 @@
         <is>
           <t>Total,0
 Tao Qichen,0
-Xu Shirong,0
 Zhao Kailiang,0</t>
         </is>
       </c>
@@ -1481,7 +1475,7 @@
 Tao Qichen,style="color:
 Wang Hao23,Submitted
 Lu Dinghao,Submitted
-Xu Shirong,style="color:
+Xu Shirong,Submitted
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
@@ -1552,14 +1546,13 @@
 Tao Qichen,100
 Wang Hao23,100
 Lu Dinghao,100
-Xu Shirong,0
+Xu Shirong,100
 Zhao Kailiang,0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>Total,0
-Xu Shirong,0
 Zhao Kailiang,0</t>
         </is>
       </c>
@@ -1574,7 +1567,7 @@
 Tao Qichen,Submitted
 Wang Hao23,Submitted
 Lu Dinghao,Submitted
-Xu Shirong,style="color:
+Xu Shirong,Submitted
 Zhao Kailiang,style="color:</t>
         </is>
       </c>

--- a/yanfeng/PKR确认信息/PKR完成情况（近两周）.xlsx
+++ b/yanfeng/PKR确认信息/PKR完成情况（近两周）.xlsx
@@ -590,7 +590,7 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Tao.Qichen@yanfeng.com,Wang23.Hao@yanfeng.com,Zhao.Kailiang@yanfeng.com</t>
+          <t>Wang23.Hao@yanfeng.com</t>
         </is>
       </c>
     </row>
@@ -654,18 +654,16 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Total,0
-Wang Hao23,0
+          <t>Total,100
+Wang Hao23,100
 Lu Dinghao,100
 Xu Shirong,100
-Zhao Kailiang,0</t>
+Zhao Kailiang,100</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Total,0
-Wang Hao23,0
-Zhao Kailiang,0</t>
+          <t>完成</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -676,10 +674,10 @@
       <c r="Q3" t="inlineStr">
         <is>
           <t>Total,Submitted
-Wang Hao23,style="color:
+Wang Hao23,Submitted
 Lu Dinghao,Submitted
 Xu Shirong,Submitted
-Zhao Kailiang,style="color:</t>
+Zhao Kailiang,Submitted</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -843,7 +841,7 @@
       <c r="Q5" t="inlineStr">
         <is>
           <t>Total,Submitted
-Wang Hao23,style="color:
+Wang Hao23,Submitted
 Lu Dinghao,Submitted
 Lu Gongchao,Submitted
 Xu Shirong,Submitted</t>
@@ -916,8 +914,8 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Total,0
-Wang Hao23,0
+          <t>Total,100
+Wang Hao23,100
 Lu Dinghao,100
 Lu Gongchao,100
 Xu Shirong,100</t>
@@ -925,8 +923,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Total,0
-Wang Hao23,0</t>
+          <t>完成</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -937,7 +934,7 @@
       <c r="Q6" t="inlineStr">
         <is>
           <t>Total,Submitted
-Wang Hao23,style="color:
+Wang Hao23,Submitted
 Lu Dinghao,Submitted
 Lu Gongchao,Submitted
 Xu Shirong,Submitted</t>
@@ -1449,126 +1446,123 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Total,0
-Tao Qichen,0
-Wang Hao23,100
-Lu Dinghao,100
-Xu Shirong,100
-Zhao Kailiang,0</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Total,0
-Tao Qichen,0
-Zhao Kailiang,0</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Tao Qichen,style="color:
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Xu Shirong,Submitted
-Zhao Kailiang,style="color:</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>未确认(cao liang)</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>30030289-EBP</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>30030289-2027,AP,Mercedes-Benz,EU V530-IP, welding, 250265, T,Equipment</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Fan Jiejie_樊皆杰(ufanj028)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Gao Yiheng01_高一恒(ugaoy160)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Phase 4 Manufacturing Development</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>45906</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>45920</v>
-      </c>
-      <c r="J13" s="1" t="n">
-        <v>45948</v>
-      </c>
-      <c r="K13" s="1" t="n">
-        <v>46157</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>2027-09-30</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Phase 4 Gate Exit-CPA</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Total,0
+          <t>Total,100
 Tao Qichen,100
 Wang Hao23,100
 Lu Dinghao,100
 Xu Shirong,100
-Zhao Kailiang,0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Total,0
-Zhao Kailiang,0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+Zhao Kailiang,100</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Total,Submitted
 Tao Qichen,Submitted
 Wang Hao23,Submitted
 Lu Dinghao,Submitted
 Xu Shirong,Submitted
-Zhao Kailiang,style="color:</t>
+Zhao Kailiang,Submitted</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>未确认(cao liang)</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>30030289-EBP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>30030289-2027,AP,Mercedes-Benz,EU V530-IP, welding, 250265, T,Equipment</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fan Jiejie_樊皆杰(ufanj028)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Gao Yiheng01_高一恒(ugaoy160)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>45906</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>45920</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>45948</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2027-09-30</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Total,100
+Tao Qichen,100
+Wang Hao23,100
+Lu Dinghao,100
+Xu Shirong,100
+Zhao Kailiang,100</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Tao Qichen,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,Submitted</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">

--- a/yanfeng/PKR确认信息/PKR完成情况（近两周）.xlsx
+++ b/yanfeng/PKR确认信息/PKR完成情况（近两周）.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,27 +520,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30035089-EBP</t>
+          <t>30035208-EBP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30035089-2026,AP,SAIC-GM,E2LB-2-IP, Automation, 260129, M,Equipment</t>
+          <t>30035208-2026,AP,Jianghuai,C673-DP,Foam Sticking,260140,M,Equipment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SAIC-GM</t>
+          <t>Jianghuai</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+          <t>Shang Bing_尚兵(ushab007)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wang Xiaoyu03_王晓宇(uwanx1357)</t>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -554,20 +554,20 @@
         </is>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46151</v>
+        <v>46162</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>46158</v>
+        <v>46173</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>46165</v>
+        <v>46186</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>46186</v>
+        <v>46221</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2027-10-29</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -583,14 +583,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>本周</t>
+          <t>下周</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Wang23.Hao@yanfeng.com</t>
+          <t>Dinghao.Lu@yanfeng.com; Gongchao.Lu@yanfeng.com; Hao.Wang23@yanfeng.com; Kailiang.Zhao@yanfeng.com; Shirong.Xu@yanfeng.com</t>
         </is>
       </c>
     </row>
@@ -654,11 +654,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Total,100
-Wang Hao23,100
-Lu Dinghao,100
-Xu Shirong,100
-Zhao Kailiang,100</t>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
+</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -673,16 +674,16 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Xu Shirong,Submitted
-Zhao Kailiang,Submitted</t>
+          <t>Total,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Xu Shirong,Confirmed
+Zhao Kailiang,Confirmed</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>未确认(cao liang)</t>
+          <t>完成确认</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
@@ -690,27 +691,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30034747-EBP</t>
+          <t>30035089-EBP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30034747-2026,AP,Huawei Anhui,X90-DP,260116,Glue spray,M,Equipment</t>
+          <t>30035089-2026,AP,SAIC-GM,E2LB-2-IP, Automation, 260129, M,Equipment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Huawei Anhui</t>
+          <t>SAIC-GM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cheng Debao_程德宝(uched025)</t>
+          <t>Wang Xiaoyu03_王晓宇(uwanx1357)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -724,7 +725,7 @@
         </is>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46158</v>
+        <v>46151</v>
       </c>
       <c r="I4" s="1" t="n">
         <v>46158</v>
@@ -733,31 +734,55 @@
         <v>46165</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>46234</v>
+        <v>46186</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2027-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Phase 1 Gate Exit-GO</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>phase1不适用</t>
+          <t>Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Total,style="color:
+Wang Hao23,style="color:
+Lu Dinghao,style="color:
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
       <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -815,59 +840,38 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Phase 2 Gate Exit-DVR</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Total,0
-Wang Hao23,0
-Lu Dinghao,100
-Lu Gongchao,100
-Xu Shirong,100</t>
-        </is>
-      </c>
+          <t>Phase 1 Gate Exit-GO</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Total,0
-Wang Hao23,0</t>
+          <t>phase1不适用</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Lu Gongchao,Submitted
-Xu Shirong,Submitted</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>未确认(cao liang)</t>
-        </is>
-      </c>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30034624-EBP</t>
+          <t>30034747-EBP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30034624-2026,AP,BYD,Lamination,260102,M,Equipment</t>
+          <t>30034747-2026,AP,Huawei Anhui,X90-DP,260116,Glue spray,M,Equipment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BYD</t>
+          <t>Huawei Anhui</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -877,7 +881,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Huang Linjian_黄琳健(uhual254)</t>
+          <t>Cheng Debao_程德宝(uched025)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -887,17 +891,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 1 Quotation</t>
         </is>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46166</v>
+        <v>46158</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>46158</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>46172</v>
+        <v>46165</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>46234</v>
@@ -914,11 +918,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Total,100
-Wang Hao23,100
-Lu Dinghao,100
-Lu Gongchao,100
-Xu Shirong,100</t>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -928,176 +933,10 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>下周</t>
+          <t>本周</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Lu Gongchao,Submitted
-Xu Shirong,Submitted</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>未确认(cao liang)</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>30034623-EBP</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>30034623-2026,AP,BYD,Glue,260103,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>BYD</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Phase 1 Quotation</t>
-        </is>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>46157</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>46164</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>46172</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>46193</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2027-09-08</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Phase 1 Gate Exit-GO</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>phase1不适用</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>30033578-EBP</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>30033578-2026,AP,Tes,TBD_Click Rim, Lami, 260050, T,Equipment</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Tes</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Zou Chengcheng_邹成成(uzouc016)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Zhou Huasheng_周华盛(uzhoh176)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Phase 2 Concept Definition</t>
-        </is>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>46137</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>46154</v>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>46185</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Phase 2 Gate Exit-DVR</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Total,100
-Wang Hao23,100
-Lu Dinghao,100
-Lu Gongchao,100
-Xu Shirong,100</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>完成</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
         <is>
           <t>Total,Confirmed
 Wang Hao23,Confirmed
@@ -1106,87 +945,432 @@
 Xu Shirong,Confirmed</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>完成确认</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>30034747-EBP</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30034747-2026,AP,Huawei Anhui,X90-DP,260116,Glue spray,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Huawei Anhui</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Cheng Debao_程德宝(uched025)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>46158</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>46158</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>46165</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2027-09-30</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Total,style="color:
+Wang Hao23,style="color:
+Lu Dinghao,style="color:
+Lu Gongchao,style="color:
+Xu Shirong,style="color:</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>30034746-EBP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30034746-2026,AP,Huawei Anhui,X90-DP,260115,glue spray,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Huawei Anhui</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Cheng Debao_程德宝(uched025)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>46165</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2027-09-25</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Phase 1 Gate Exit-GO</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>phase1不适用</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>30033404-EBP</t>
+          <t>30034746-EBP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30033404-2026,AP,VW Group,VW426-DP,Lamination,260033,M,Equipment</t>
+          <t>30034746-2026,AP,Huawei Anhui,X90-DP,260115,glue spray,M,Equipment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VW Group</t>
+          <t>Huawei Anhui</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
+          <t>Shang Bing_尚兵(ushab007)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Cheng Debao_程德宝(uched025)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>46165</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2027-09-25</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Total,style="color:
+Wang Hao23,style="color:
+Lu Dinghao,style="color:
+Lu Gongchao,style="color:
+Xu Shirong,style="color:</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>30034624-EBP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>30034624-2026,AP,BYD,Lamination,260102,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BYD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Huang Linjian_黄琳健(uhual254)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Phase 3 Design Feasibility</t>
-        </is>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>46093</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>46121</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>46152</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <v>46182</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Phase 3 Gate Exit-FPR</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Total,100
-Wang Hao23,100
-Lu Dinghao,100
-Lu Gongchao,100
-Xu Shirong,100</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>46158</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2027-09-30</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Phase 1 Gate Exit-GO</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>phase1不适用</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>30034624-EBP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>30034624-2026,AP,BYD,Lamination,260102,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BYD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>46158</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2027-09-30</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>本周</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Total,Confirmed
 Wang Hao23,Confirmed
@@ -1195,185 +1379,1565 @@
 Xu Shirong,Confirmed</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>完成确认</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>30032706-EBP</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>30032706-2025,AP,SERES Motors,A15-mirror, assy, 260006, 15T,Equipment</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>SERES Motors</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Wang Baowei_王保卫(uwanb363)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Wang Wanfang_王万芳(uwanw356)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>30034623-EBP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>30034623-2026,AP,BYD,Glue,260103,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BYD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Xu Shirong_徐时荣(uxuxs004)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Phase 1 Quotation</t>
         </is>
       </c>
-      <c r="H10" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>46152</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="K10" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="H12" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2027-09-08</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Phase 1 Gate Exit-GO</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>phase1不适用</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>30034623-EBP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>30034623-2026,AP,BYD,Glue,260103,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BYD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2027-09-08</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>Phase 2 Gate Exit-DVR</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Total,90
-Wang Hao23,100
-Lu Dinghao,100
-Xu Shirong,90
-Zhao Kailiang,100</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,style="color:
+Lu Gongchao,style="color:
+Xu Shirong,style="color:</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>30034480-EBP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>30034480-2028,AP,Toyota,780B,Spraying,260086,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Chen Ziyi01_陈子翌(uchez443)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phase0</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>46138</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Total,style="color:
+Wang Hao23,style="color:
+Lu Dinghao,style="color:
+Lu Gongchao,style="color:
+Xu Shirong,style="color:</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>30034479-EBP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>30034479-2027,AP,Toyota,780B,Spraying,260085,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phase0</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>46138</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Total,style="color:
+Wang Hao23,style="color:
+Lu Dinghao,style="color:
+Lu Gongchao,style="color:
+Xu Shirong,style="color:</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>30034478-EBP</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>30034478-2026,AP,Toyota,780B-DP, flaming,260080,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Zhang Shuai27_张帅(uzhas1129)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>46138</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Total,style="color:
+Wang Hao23,style="color:
+Lu Dinghao,style="color:
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>30034477-EBP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>30034477-2025,AP,Toyota,780B-DP,Flaming, 260079,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>46138</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Total,style="color:
+Wang Hao23,style="color:
+Lu Dinghao,style="color:
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>30033578-EBP</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>30033578-2026,AP,Tes,TBD_Click Rim, Lami, 260050, T,Equipment</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Tes</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Zhou Huasheng_周华盛(uzhoh176)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>46137</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>本周</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Total,Confirmed
 Wang Hao23,Confirmed
 Lu Dinghao,Confirmed
-Xu Shirong,Confirmed
-Zhao Kailiang,Confirmed</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
+Lu Gongchao,Confirmed
+Xu Shirong,Confirmed</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>完成确认</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>30033376-EBP</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>30033376-2026,AP,Huawei Anhui,F05&amp;F03,Assembly,260031,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Huawei Anhui</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>46101</v>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Total,style="color:
+Wang Hao23,style="color:
+Lu Dinghao,style="color:
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>30033375-EBP</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>30033375-2026,AP,Huawei Anhui,F05&amp;F03,Assembly,260032，T,Equipment</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Huawei Anhui</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="I20" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="J20" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>30033373-EBP</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>30033373-2026,AP,Huawei Anhui,F03F05,Assembly,260030,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Huawei Anhui</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="J21" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>30032991-EBP</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>30032991-2026,AP,Jianghuai,JH-C-mirror,assembly,260009,14T,Equipment</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Jianghuai</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Zhang Shuai27_张帅(uzhas1129)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="I22" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="J22" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Total,style="color:
+Wang Hao23,style="color:
+Lu Dinghao,style="color:
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>30032988-EBP</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>30032988-2026,AP,SERES Motors,V32-mirror,Assembly,260007, 14T,Equipment</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SERES Motors</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Guo Xinjie_郭新杰(uguox097)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="J23" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Total,style="color:
+Wang Hao23,style="color:
+Lu Dinghao,style="color:
+Xu Shirong,style="color:
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>30031526-EBP</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>30031526-2027,EMEA,Mercedes-Benz,EU V530 CUN,pre-fixing,250335,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Fan Jiejie_樊皆杰(ufanj028)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Chen Yuhang03_陈雨杭(uchey949)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>45981</v>
+      </c>
+      <c r="I24" s="1" t="n">
+        <v>46011</v>
+      </c>
+      <c r="J24" s="1" t="n">
+        <v>46011</v>
+      </c>
+      <c r="K24" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2027-09-01</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Total,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Lu Gongchao,Confirmed
+Xu Shirong,Confirmed</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>完成确认</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>30031525-EBP</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>30031525-2027,EMEA,Mercedes-Benz,EU V530-cun,pre-fixing,250334,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Fan Jiejie_樊皆杰(ufanj028)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>45981</v>
+      </c>
+      <c r="I25" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="J25" s="1" t="n">
+        <v>46011</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2027-09-01</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Total,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Lu Gongchao,Confirmed
+Xu Shirong,Confirmed</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>完成确认</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>30030383-EBP</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>30030383-2027,AP,Mercedes-Benz,EU V530-CUN,Lamination,250275,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Fan Jiejie_樊皆杰(ufanj028)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Huang Dongfang01_黄东方(uhuad056)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>45906</v>
+      </c>
+      <c r="I26" s="1" t="n">
+        <v>45913</v>
+      </c>
+      <c r="J26" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="K26" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2027-09-30</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Total,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Lu Gongchao,Confirmed
+Xu Shirong,Confirmed</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>完成确认</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>30030382-EBP</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>30030382-2027,AP,Mercedes-Benz,EU V530 - CUN, glue spray, T,Equipment</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Fan Jiejie_樊皆杰(ufanj028)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>45913</v>
+      </c>
+      <c r="I27" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="J27" s="1" t="n">
+        <v>46021</v>
+      </c>
+      <c r="K27" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2027-09-30</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Total,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Lu Gongchao,Confirmed
+Xu Shirong,Confirmed</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>完成确认</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>30030292-EBP</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>30030292-2027,AP,Mercedes-Benz,EU V530-IP,welding,250267,M,Equipment</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Mercedes-Benz</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Fan Jiejie_樊皆杰(ufanj028)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Hao Xiuxia_郝秀霞(uhaox031)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Xu Shirong_徐时荣(uxuxs004)</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="H28" s="1" t="n">
         <v>45900</v>
       </c>
-      <c r="I11" s="1" t="n">
+      <c r="I28" s="1" t="n">
         <v>45905</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J28" s="1" t="n">
         <v>45928</v>
       </c>
-      <c r="K11" s="1" t="n">
+      <c r="K28" s="1" t="n">
         <v>46157</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>2027-06-30</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Total,100
-Tao Qichen,100
-Wang Hao23,100
-Lu Dinghao,100
-Xu Shirong,100
-Zhao Kailiang,100</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="N28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Tao Qichen的PKR打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Total,Confirmed
 Tao Qichen,Confirmed
@@ -1383,194 +2947,196 @@
 Zhao Kailiang,Confirmed</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>完成确认</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>30030290-EBP</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>30030290-2027,AP,Mercedes-Benz,EU V530-IP, welding, 250266, T,Equipment</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Mercedes-Benz</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Fan Jiejie_樊皆杰(ufanj028)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Min Hongen_闵宏恩(uminh009)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
         <is>
           <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
-      <c r="H12" s="1" t="n">
+      <c r="H29" s="1" t="n">
         <v>45906</v>
       </c>
-      <c r="I12" s="1" t="n">
+      <c r="I29" s="1" t="n">
         <v>45920</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J29" s="1" t="n">
         <v>45981</v>
       </c>
-      <c r="K12" s="1" t="n">
+      <c r="K29" s="1" t="n">
         <v>46157</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>2027-09-30</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Total,100
-Tao Qichen,100
-Wang Hao23,100
-Lu Dinghao,100
-Xu Shirong,100
-Zhao Kailiang,100</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
+      <c r="N29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Tao Qichen的PKR打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Tao Qichen,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Xu Shirong,Submitted
-Zhao Kailiang,Submitted</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>未确认(cao liang)</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Total,Confirmed
+Tao Qichen,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Xu Shirong,Confirmed
+Zhao Kailiang,Confirmed</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>完成确认</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>30030289-EBP</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>30030289-2027,AP,Mercedes-Benz,EU V530-IP, welding, 250265, T,Equipment</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Mercedes-Benz</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Fan Jiejie_樊皆杰(ufanj028)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Gao Yiheng01_高一恒(ugaoy160)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
         <is>
           <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="H30" s="1" t="n">
         <v>45906</v>
       </c>
-      <c r="I13" s="1" t="n">
+      <c r="I30" s="1" t="n">
         <v>45920</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J30" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="K13" s="1" t="n">
+      <c r="K30" s="1" t="n">
         <v>46157</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>2027-09-30</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Total,100
-Tao Qichen,100
-Wang Hao23,100
-Lu Dinghao,100
-Xu Shirong,100
-Zhao Kailiang,100</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="N30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Tao Qichen的PKR打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Tao Qichen,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Xu Shirong,Submitted
-Zhao Kailiang,Submitted</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>未确认(cao liang)</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Total,Confirmed
+Tao Qichen,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Xu Shirong,Confirmed
+Zhao Kailiang,Confirmed</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>完成确认</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/yanfeng/PKR确认信息/PKR完成情况（近两周）.xlsx
+++ b/yanfeng/PKR确认信息/PKR完成情况（近两周）.xlsx
@@ -590,7 +590,7 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Dinghao.Lu@yanfeng.com; Gongchao.Lu@yanfeng.com; Hao.Wang23@yanfeng.com; Kailiang.Zhao@yanfeng.com; Shirong.Xu@yanfeng.com</t>
+          <t>Dinghao.Lu@yanfeng.com; Gongchao.Lu@yanfeng.com; Kailiang.Zhao@yanfeng.com; Shirong.Xu@yanfeng.com</t>
         </is>
       </c>
     </row>
@@ -749,19 +749,16 @@
       <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
 Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；
+Zhao Kailiang的PKR打分：100；
 </t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -771,11 +768,11 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
 Xu Shirong,style="color:
-Zhao Kailiang,style="color:</t>
+Zhao Kailiang,Submitted</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1013,8 +1010,8 @@
       <c r="N7" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
 Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；
 </t>
@@ -1022,9 +1019,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
+          <t>Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
@@ -1035,9 +1030,9 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
 Lu Gongchao,style="color:
 Xu Shirong,style="color:</t>
         </is>
@@ -1183,8 +1178,8 @@
       <c r="N9" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
 Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；
 </t>
@@ -1192,9 +1187,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
+          <t>Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
@@ -1205,9 +1198,9 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
 Lu Gongchao,style="color:
 Xu Shirong,style="color:</t>
         </is>
@@ -1521,25 +1514,115 @@
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>30034480-EBP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>30034480-2028,AP,Toyota,780B,Spraying,260086,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Chen Ziyi01_陈子翌(uchez443)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phase0</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>46138</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：0；
 Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；
 </t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Lu Dinghao的PKR打分：0；
 Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>本周</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
@@ -1548,99 +1631,6 @@
 Xu Shirong,style="color:</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>30034480-EBP</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>30034480-2028,AP,Toyota,780B,Spraying,260086,T,Equipment</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Toyota</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Chen Ziyi01_陈子翌(uchez443)</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Phase0</t>
-        </is>
-      </c>
-      <c r="H14" s="1" t="n">
-        <v>46138</v>
-      </c>
-      <c r="I14" s="1" t="n">
-        <v>46166</v>
-      </c>
-      <c r="J14" s="1" t="n">
-        <v>46197</v>
-      </c>
-      <c r="K14" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Phase 2 Gate Exit-DVR</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
-Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
-        </is>
-      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
@@ -1705,8 +1695,8 @@
       <c r="N15" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
 Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；
 </t>
@@ -1714,9 +1704,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
+          <t>Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
@@ -1727,9 +1715,9 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
 Lu Gongchao,style="color:
 Xu Shirong,style="color:</t>
         </is>
@@ -1798,7 +1786,7 @@
       <c r="N16" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
+Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：0；
 Xu Shirong的PKR打分：0；
 Zhao Kailiang的PKR打分：0；
@@ -1807,8 +1795,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
+          <t>Lu Dinghao的PKR打分：0；
 Xu Shirong的PKR打分：0；
 Zhao Kailiang的PKR打分：0；</t>
         </is>
@@ -1820,8 +1807,8 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
 Lu Dinghao,style="color:
 Xu Shirong,style="color:
 Zhao Kailiang,style="color:</t>
@@ -1891,8 +1878,8 @@
       <c r="N17" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
 Xu Shirong的PKR打分：0；
 Zhao Kailiang的PKR打分：0；
 </t>
@@ -1900,9 +1887,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
+          <t>Xu Shirong的PKR打分：0；
 Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
@@ -1913,9 +1898,9 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
 Xu Shirong,style="color:
 Zhao Kailiang,style="color:</t>
         </is>
@@ -2078,19 +2063,16 @@
       <c r="N19" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
 Zhao Kailiang的PKR打分：0；
 </t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2100,10 +2082,10 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
-Xu Shirong,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
@@ -2173,15 +2155,14 @@
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：0；
+Xu Shirong的PKR打分：100；
 Zhao Kailiang的PKR打分：0；
 </t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2194,7 +2175,7 @@
           <t>Total,Submitted
 Wang Hao23,Submitted
 Lu Dinghao,Submitted
-Xu Shirong,style="color:
+Xu Shirong,Submitted
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
@@ -2264,15 +2245,14 @@
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：0；
+Xu Shirong的PKR打分：100；
 Zhao Kailiang的PKR打分：0；
 </t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2285,7 +2265,7 @@
           <t>Total,Submitted
 Wang Hao23,Submitted
 Lu Dinghao,Submitted
-Xu Shirong,style="color:
+Xu Shirong,Submitted
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
@@ -2353,19 +2333,16 @@
       <c r="N22" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
 Zhao Kailiang的PKR打分：0；
 </t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2375,10 +2352,10 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
-Xu Shirong,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
 Zhao Kailiang,style="color:</t>
         </is>
       </c>
@@ -2446,19 +2423,16 @@
       <c r="N23" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
 Zhao Kailiang的PKR打分：0；
 </t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2468,10 +2442,10 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
-Xu Shirong,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
 Zhao Kailiang,style="color:</t>
         </is>
       </c>

--- a/yanfeng/PKR确认信息/PKR完成情况（近两周）.xlsx
+++ b/yanfeng/PKR确认信息/PKR完成情况（近两周）.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,7 +616,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Dinghao.Lu@yanfeng.com; Gongchao.Lu@yanfeng.com; Hao.Wang23@yanfeng.com; Kailiang.Zhao@yanfeng.com; Shirong.Xu@yanfeng.com</t>
+          <t>Gongchao.Lu@yanfeng.com; Kailiang.Zhao@yanfeng.com</t>
         </is>
       </c>
     </row>
@@ -827,58 +827,62 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30033404-EBP</t>
+          <t>30032991-EBP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30033404-2026,AP,VW Group,VW426-DP,Lamination,260033,M,Equipment</t>
+          <t>30032991-2026,AP,Jianghuai,JH-C-mirror,assembly,260009,14T,Equipment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VW Group</t>
+          <t>Jianghuai</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Huang Linjian_黄琳健(uhual254)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>Zhang Shuai27_张帅(uzhas1129)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -887,106 +891,6 @@
         </is>
       </c>
       <c r="N5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：100；
-Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,style="color:
-Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>30033723-EBP</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>30033723-2026,AP,VW Group,VW426 PAB Chute Cell CI,260042,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>VW Group</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Wei Shaoguan_韦少官(uweis086)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Phase 2 Concept Definition</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Phase 3 Gate Exit-FPR</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：100；
 Wang Hao23的PKR打分：100；
@@ -996,6 +900,108 @@
 </t>
         </is>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Total,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Xu Shirong,Confirmed
+Zhao Kailiang,Confirmed</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>完成确认</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>30032991-EBP</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>30032991-2026,AP,Jianghuai,JH-C-mirror,assembly,260009,14T,Equipment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Jianghuai</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Zhang Shuai27_张帅(uzhas1129)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>完成</t>
@@ -1008,16 +1014,16 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Xu Shirong,Submitted
-Zhao Kailiang,Submitted</t>
+          <t>Total,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Xu Shirong,Confirmed
+Zhao Kailiang,Confirmed</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>未确认(Cao Liang)</t>
+          <t>完成确认</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
@@ -1025,85 +1031,78 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>30033578-EBP</t>
+          <t>30033404-EBP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30033578-2026,AP,Tes,TBD_Click Rim, Lami, 260050, T,Equipment</t>
+          <t>30033404-2026,AP,VW Group,VW426-DP,Lamination,260033,M,Equipment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tes</t>
+          <t>VW Group</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zhou Huasheng_周华盛(uzhoh176)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Phase 3 Gate Exit-FPR</t>
+          <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
 Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；
+Xu Shirong的PKR打分：100；
 </t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
+          <t>Lu Gongchao的PKR打分：0；</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1113,11 +1112,11 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
 Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
+Xu Shirong,Submitted</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1130,102 +1129,97 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>30035089-EBP</t>
+          <t>30033723-EBP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30035089-2026,AP,SAIC-GM,E2LB-2-IP, Automation, 260129, M,Equipment</t>
+          <t>30033723-2026,AP,VW Group,VW426 PAB Chute Cell CI,260042,M,Equipment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SAIC-GM</t>
+          <t>VW Group</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wang Xiaoyu03_王晓宇(uwanx1357)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
+          <t>Wei Shaoguan_韦少官(uweis086)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Phase 4 Gate Exit-CPA</t>
+          <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">最低打分：0；
+          <t xml:space="preserve">最低打分：100；
 Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
 </t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>完成</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>下周</t>
+          <t>本周</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Xu Shirong,style="color:
-Zhao Kailiang,style="color:</t>
+          <t>Total,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Xu Shirong,Confirmed
+Zhao Kailiang,Confirmed</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>未评分(工程师)</t>
+          <t>完成确认</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -1233,62 +1227,266 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>30033578-EBP</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>30033578-2026,AP,Tes,TBD_Click Rim, Lami, 260050, T,Equipment</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Tes</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Zhou Huasheng_周华盛(uzhoh176)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>30035089-EBP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>30035089-2026,AP,SAIC-GM,E2LB-2-IP, Automation, 260129, M,Equipment</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SAIC-GM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Wang Xiaoyu03_王晓宇(uwanx1357)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Total,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Xu Shirong,Confirmed
+Zhao Kailiang,Confirmed</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>完成确认</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>30035325-EBP</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>30035325-2026,AP,SERES Motors,遮阳板,1200压机,260145,1M,Equipment</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>SERES Motors</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Meng Zibing_孟子冰(umenz002)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：100；
 Wang Hao23的PKR打分：100；
@@ -1298,17 +1496,17 @@
 </t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>本周</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Total,Confirmed
 Wang Hao23,Confirmed
@@ -1317,80 +1515,80 @@
 Xu Shirong,Confirmed</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>完成确认</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>30034746-EBP</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>30034746-2026,AP,Huawei Anhui,X90-DP,260115,glue spray,M,Equipment</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Huawei Anhui</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Shang Bing_尚兵(ushab007)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Cheng Debao_程德宝(uched025)</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Xu Shirong_徐时荣(uxuxs004)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>2026-05-24</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>2027-09-25</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：100；
 Wang Hao23的PKR打分：100；
@@ -1400,17 +1598,17 @@
 </t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>本周</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Total,Confirmed
 Wang Hao23,Confirmed
@@ -1419,80 +1617,80 @@
 Xu Shirong,Confirmed</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>完成确认</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>30034166-EBP</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>30034166-2026,AP,SAIC-GM,C1UL-2,CNSL,Lamination,260073,T,Equipment</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>SAIC-GM</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Shang Bing_尚兵(ushab007)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Fan Aiqiang01_樊爱强(ufana018)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Xu Shirong_徐时荣(uxuxs004)</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Phase 2 Concept Definition</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Phase 2 Gate Exit-DVR</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：100；
@@ -1502,17 +1700,17 @@
 </t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Lu Gongchao的PKR打分：0；</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,Submitted
@@ -1521,209 +1719,27 @@
 Xu Shirong,Submitted</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>30035209-EBP</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>30035209-2026,AP,Jianghuai,C673-DP,Foam sticking,T,Equipment</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Jianghuai</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Chen Zhibin01_陈志斌(uchez368)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Phase 1 Quotation</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2027-10-31</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Phase 2 Gate Exit-DVR</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；
-</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Total,style="color:
-Wang Hao23,style="color:
-Lu Dinghao,style="color:
-Xu Shirong,style="color:
-Zhao Kailiang,style="color:</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>30017341-EBP</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>30017341-2024,AP,BYD,SA5-IP,Lamination,220281,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>BYD</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Liu Cong02_刘聪(uliuc396)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Phase 1 Quotation</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Phase 1 Gate Exit-GO</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>phase1不适用</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>本周</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>30034578-EBP</t>
+          <t>30035209-EBP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>30034578-2026,AP,BYD,Glue,260093,M,Equipment</t>
+          <t>30035209-2026,AP,Jianghuai,C673-DP,Foam sticking,T,Equipment</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BYD</t>
+          <t>Jianghuai</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1733,7 +1749,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1748,116 +1764,218 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2027-10-31</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Phase 1 Gate Exit-GO</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：0；
+</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>phase1不适用</t>
+          <t>Zhao Kailiang的PKR打分：0；</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>本周</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,style="color:</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>30034578-EBP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>30034578-2026,AP,BYD,Glue,260093,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BYD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Phase 1 Gate Exit-GO</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>phase1不适用</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>30035208-EBP</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>30035208-2026,AP,Jianghuai,C673-DP,Foam Sticking,260140,M,Equipment</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Jianghuai</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Shang Bing_尚兵(ushab007)</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Chen Zhibin01_陈志斌(uchez368)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Xu Shirong_徐时荣(uxuxs004)</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Phase 1 Quotation</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>2027-10-29</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Phase 2 Gate Exit-DVR</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：100；
 Wang Hao23的PKR打分：100；
@@ -1867,17 +1985,17 @@
 </t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>本周</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Total,Confirmed
 Wang Hao23,Confirmed
@@ -1886,108 +2004,27 @@
 Zhao Kailiang,Confirmed</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>完成确认</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>30035208-EBP</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>30035208-2026,AP,Jianghuai,C673-DP,Foam Sticking,260140,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Jianghuai</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Chen Zhibin01_陈志斌(uchez368)</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Phase 1 Quotation</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>2027-10-29</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Phase 1 Gate Exit-GO</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>phase1不适用</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>本周</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>30034577-EBP</t>
+          <t>30035208-EBP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30034577-2026,AP,BYD,EHX,Glue,260088,M,Equipment</t>
+          <t>30035208-2026,AP,Jianghuai,C673-DP,Foam Sticking,260140,M,Equipment</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BYD</t>
+          <t>Jianghuai</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1997,7 +2034,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2017,22 +2054,22 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2027-10-29</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2058,12 +2095,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>30034579-EBP</t>
+          <t>30034577-EBP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30034579-2026,AP,BYD,Glue,260095,M,Equipment</t>
+          <t>30034577-2026,AP,BYD,EHX,Glue,260088,M,Equipment</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2093,27 +2130,27 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2129,7 +2166,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>下周</t>
+          <t>本周</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
@@ -2139,32 +2176,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>30035188-EBP</t>
+          <t>30017341-EBP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>30035188-2026,AP,smartmi,KUNLUN-light,welding.260135.M,Equipment</t>
+          <t>30017341-2024,AP,BYD,SA5-IP,Lamination,220281,M,Equipment</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>smartmi</t>
+          <t>BYD</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Chen Jiarong_陈佳荣(uchej731)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Wei Shaoguan_韦少官(uweis086)</t>
-        </is>
-      </c>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+          <t>Liu Cong02_刘聪(uliuc396)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2174,7 +2207,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2194,7 +2227,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2210,7 +2243,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>下周</t>
+          <t>本周</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
@@ -2220,27 +2253,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>30035096-EBP</t>
+          <t>30034579-EBP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>30035096-2026,AP,smartmi,F2N-light,welding260130,M,Equipment</t>
+          <t>30034579-2026,AP,BYD,Glue,260095,M,Equipment</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>smartmi</t>
+          <t>BYD</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Chen Jiarong_陈佳荣(uchej731)</t>
+          <t>Shang Bing_尚兵(ushab007)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wei Shaoguan_韦少官(uweis086)</t>
+          <t>Chen Jie04_陈洁(uchej018)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2255,27 +2288,27 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2301,30 +2334,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>30035236-EBP</t>
+          <t>30035188-EBP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>30035236-2026,NA,Ford,P703-Airbag, assembly, 260142,1T,Equipment</t>
+          <t>30035188-2026,AP,smartmi,KUNLUN-light,welding.260135.M,Equipment</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>smartmi</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Wang Baowei_王保卫(uwanb363)</t>
+          <t>Chen Jiarong_陈佳荣(uchej731)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Huang Dinghui_黄定辉(uhuad002)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>Wei Shaoguan_韦少官(uweis086)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Phase 1 Quotation</t>
@@ -2332,27 +2369,27 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2374,6 +2411,164 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>30035096-EBP</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>30035096-2026,AP,smartmi,F2N-light,welding260130,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>smartmi</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Chen Jiarong_陈佳荣(uchej731)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Wei Shaoguan_韦少官(uweis086)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Phase 1 Gate Exit-GO</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>phase1不适用</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>30035236-EBP</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>30035236-2026,NA,Ford,P703-Airbag, assembly, 260142,1T,Equipment</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Huang Dinghui_黄定辉(uhuad002)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Phase 1 Gate Exit-GO</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>phase1不适用</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/yanfeng/PKR确认信息/PKR完成情况（近两周）.xlsx
+++ b/yanfeng/PKR确认信息/PKR完成情况（近两周）.xlsx
@@ -516,17 +516,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30033723-EBP</t>
+          <t>30030313-EBP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30033723-2026,AP,VW Group,VW426 PAB Chute Cell CI,260042,M,Equipment</t>
+          <t>30030313-2026,AP,Tes,Highland-FC,Assembly,250268,3T,Equipment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VW Group</t>
+          <t>Tes</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -536,46 +536,258 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wei Shaoguan_韦少官(uweis086)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>Li Yanchen_李彦辰(ulixy466)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Zhou Meijiao01_周美娇(uzhom121)</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,style="color:
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,Submitted</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Gongchao.Lu@yanfeng.com; Hao.Wang23@yanfeng.com; Shirong.Xu@yanfeng.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>30034171-EBP</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30034171-2026,AP,Jianghuai,JHC-sun visor,assy, 260074, NT,Equipment</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Jianghuai</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,style="color:
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,Submitted</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>30034168-EBP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30034168-2026,AP,SVW,A-SUV-mirror,assembly,260008,15T,Equipment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SVW</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Zhou Liwen_周理文(uzhol008)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：100；
 Wang Hao23的PKR打分：100；
@@ -585,17 +797,17 @@
 </t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>本周</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Total,Confirmed
 Wang Hao23,Confirmed
@@ -604,220 +816,9 @@
 Zhao Kailiang,Confirmed</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>完成确认</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Gongchao.Lu@yanfeng.com; Hao.Wang23@yanfeng.com; Kailiang.Zhao@yanfeng.com; Shirong.Xu@yanfeng.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>30034171-EBP</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>30034171-2026,AP,Jianghuai,JHC-sun visor,assy, 260074, NT,Equipment</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Jianghuai</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Wang Baowei_王保卫(uwanb363)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Chen Zhibin01_陈志斌(uchez368)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Phase 4 Manufacturing Development</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Phase 4 Gate Exit-CPA</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；
-</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Wang Hao23的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,style="color:
-Lu Dinghao,Submitted
-Xu Shirong,style="color:
-Zhao Kailiang,style="color:</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>30034168-EBP</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>30034168-2026,AP,SVW,A-SUV-mirror,assembly,260008,15T,Equipment</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SVW</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Wang Baowei_王保卫(uwanb363)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Zhou Liwen_周理文(uzhol008)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Phase 3 Design Feasibility</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Phase 4 Gate Exit-CPA</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：100；
-Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；
-</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Xu Shirong,style="color:
-Zhao Kailiang,style="color:</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
@@ -825,34 +826,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30034746-EBP</t>
+          <t>30034480-EBP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30034746-2026,AP,Huawei Anhui,X90-DP,260115,glue spray,M,Equipment</t>
+          <t>30034480-2028,AP,Toyota,780B,Spraying,260086,T,Equipment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Huawei Anhui</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cheng Debao_程德宝(uched025)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
+          <t>Chen Ziyi01_陈子翌(uchez443)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Phase 3 Design Feasibility</t>
@@ -860,27 +857,27 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>2026-05-24</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2027-09-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -891,7 +888,7 @@
       <c r="N5" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：100；
+Wang Hao23的PKR打分：0；
 Lu Dinghao的PKR打分：100；
 Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；
@@ -900,7 +897,8 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Lu Gongchao的PKR打分：0；
+          <t>Wang Hao23的PKR打分：0；
+Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
@@ -912,7 +910,7 @@
       <c r="Q5" t="inlineStr">
         <is>
           <t>Total,Submitted
-Wang Hao23,Submitted
+Wang Hao23,style="color:
 Lu Dinghao,Submitted
 Lu Gongchao,style="color:
 Xu Shirong,style="color:</t>
@@ -928,22 +926,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30034579-EBP</t>
+          <t>30034479-EBP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30034579-2026,AP,BYD,Glue,260095,M,Equipment</t>
+          <t>30034479-2027,AP,Toyota,780B,Spraying,260085,M,Equipment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BYD</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -951,11 +949,7 @@
           <t>Chen Jie04_陈洁(uchej018)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Phase 2 Concept Definition</t>
@@ -963,32 +957,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Phase 2 Gate Exit-DVR</t>
+          <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1008,7 +1002,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>本周</t>
+          <t>下周</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1030,27 +1024,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>30035236-EBP</t>
+          <t>30034479-EBP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30035236-2026,NA,Ford,P703-Airbag, assembly, 260142,1T,Equipment</t>
+          <t>30034479-2027,AP,Toyota,780B,Spraying,260085,M,Equipment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wang Baowei_王保卫(uwanb363)</t>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Huang Dinghui_黄定辉(uhuad002)</t>
+          <t>Chen Jie04_陈洁(uchej018)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -1061,137 +1055,35 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Phase 2 Gate Exit-DVR</t>
+          <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：100；
-Wang Hao23的PKR打分：100；
-Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：100；
-Zhao Kailiang的PKR打分：100；
-</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>完成</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>本周</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Total,Confirmed
-Wang Hao23,Confirmed
-Lu Dinghao,Confirmed
-Xu Shirong,Confirmed
-Zhao Kailiang,Confirmed</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>完成确认</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>30035162-EBP</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>30035162-2026,AP,BJEV,X90,Lamination,260133,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>BJEV</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Phase 2 Concept Definition</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2027-10-20</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Phase 3 Gate Exit-FPR</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：0；
@@ -1201,19 +1093,19 @@
 </t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Wang Hao23的PKR打分：0；
 Lu Gongchao的PKR打分：0；
 Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Total,Submitted
 Wang Hao23,style="color:
@@ -1222,6 +1114,105 @@
 Xu Shirong,style="color:</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>30034477-EBP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30034477-2025,AP,Toyota,780B-DP,Flaming, 260079,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Wang Hao23的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,style="color:
+Lu Dinghao,Submitted
+Xu Shirong,style="color:
+Zhao Kailiang,Submitted</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
@@ -1232,27 +1223,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>30033911-EBP</t>
+          <t>30034746-EBP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30033911-2026,NA,Stellantis,WL-DP,laminnation,260060,T,Equipment</t>
+          <t>30034746-2026,AP,Huawei Anhui,X90-DP,260115,glue spray,M,Equipment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Huawei Anhui</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wang Xiang02_王翔(uwanx029)</t>
+          <t>Shang Bing_尚兵(ushab007)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jin Yulong01_金宇隆(ujiny132)</t>
+          <t>Cheng Debao_程德宝(uched025)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1262,37 +1253,37 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-09-25</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Phase 2 Gate Exit-DVR</t>
+          <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1317,16 +1308,16 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Total,Submitted
-Wang Hao23,Submitted
-Lu Dinghao,Submitted
-Lu Gongchao,Submitted
-Xu Shirong,Submitted</t>
+          <t>Total,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Lu Gongchao,Confirmed
+Xu Shirong,Confirmed</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>未确认(Cao Liang)</t>
+          <t>完成确认</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -1334,27 +1325,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>30033911-EBP</t>
+          <t>30035162-EBP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>30033911-2026,NA,Stellantis,WL-DP,laminnation,260060,T,Equipment</t>
+          <t>30035162-2026,AP,BJEV,X90,Lamination,260133,M,Equipment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>BJEV</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wang Xiang02_王翔(uwanx029)</t>
+          <t>Shang Bing_尚兵(ushab007)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jin Yulong01_金宇隆(ujiny132)</t>
+          <t>Chen Jie04_陈洁(uchej018)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1364,37 +1355,37 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-10-20</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Phase 4 Gate Exit-CPA</t>
+          <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1402,16 +1393,14 @@
           <t xml:space="preserve">最低打分：0；
 Wang Hao23的PKR打分：0；
 Lu Dinghao的PKR打分：100；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；
+Lu Gongchao的PKR打分：100；
+Xu Shirong的PKR打分：100；
 </t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
+          <t>Wang Hao23的PKR打分：0；</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1424,8 +1413,8 @@
           <t>Total,Submitted
 Wang Hao23,style="color:
 Lu Dinghao,Submitted
-Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
+Lu Gongchao,Submitted
+Xu Shirong,Submitted</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1438,27 +1427,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>30036039-EBP</t>
+          <t>30036184-EBP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30036039-2026,AP,SERES Motors,L97-DAB, Lamination, 260171, 1T,Equipment</t>
+          <t>30036184-2026,AP,JAC-VW,JHB-sunvisor,assem, 260180, 2T,Equipment</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SERES Motors</t>
+          <t>JAC-VW</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Huang Dongfang01_黄东方(uhuad056)</t>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1468,71 +1457,72 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Phase 2 Gate Exit-DVR</t>
+          <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">最低打分：100；
-Wang Hao23的PKR打分：100；
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
 Lu Dinghao的PKR打分：100；
-Lu Gongchao的PKR打分：100；
-Xu Shirong的PKR打分：100；
+Xu Shirong的PKR打分：0；
+Zhao Kailiang的PKR打分：100；
 </t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>完成</t>
+          <t>Wang Hao23的PKR打分：0；
+Xu Shirong的PKR打分：0；</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>本周</t>
+          <t>下周</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>Total,Submitted
-Wang Hao23,Submitted
+Wang Hao23,style="color:
 Lu Dinghao,Submitted
-Lu Gongchao,Submitted
-Xu Shirong,Submitted</t>
+Xu Shirong,style="color:
+Zhao Kailiang,Submitted</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>未确认(Cao Liang)</t>
+          <t>未评分(工程师)</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -1600,13 +1590,13 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Phase 2 Gate Exit-DVR</t>
+          <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">最低打分：100；
-Wang Hao23的PKR打分：100；
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：0；
 Lu Dinghao的PKR打分：100；
 Xu Shirong的PKR打分：100；
 Zhao Kailiang的PKR打分：100；
@@ -1615,7 +1605,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>完成</t>
+          <t>Wang Hao23的PKR打分：0；</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1625,16 +1615,16 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Total,Confirmed
-Wang Hao23,Confirmed
-Lu Dinghao,Confirmed
-Xu Shirong,Confirmed
-Zhao Kailiang,Confirmed</t>
+          <t>Total,Submitted
+Wang Hao23,style="color:
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,Submitted</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>完成确认</t>
+          <t>未评分(工程师)</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -1642,17 +1632,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>30035707-EBP</t>
+          <t>30036085-EBP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>30035707-2026,AP,Brilliance-BMW,RGB 8PIN-light,assemble,260156,T,Equipment</t>
+          <t>30036085-2026,AP,SERES Motors,L97-light，assemble,260173,T,Equipment</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brilliance-BMW</t>
+          <t>SERES Motors</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1662,7 +1652,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zhou Liwen_周理文(uzhol008)</t>
+          <t>Huang Sheng02_黄圣(uhuas068)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1677,70 +1667,47 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Phase 3 Gate Exit-FPR</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；
-</t>
-        </is>
-      </c>
+          <t>Phase 1 Gate Exit-GO</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：0；</t>
+          <t>phase1不适用</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>本周</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,style="color:
-Lu Dinghao,Submitted
-Xu Shirong,style="color:
-Zhao Kailiang,style="color:</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
     </row>
   </sheetData>

--- a/yanfeng/PKR确认信息/PKR完成情况（近两周）.xlsx
+++ b/yanfeng/PKR确认信息/PKR完成情况（近两周）.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,278 +516,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30030313-EBP</t>
+          <t>30029284-EBP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30030313-2026,AP,Tes,Highland-FC,Assembly,250268,3T,Equipment</t>
+          <t>30029284-2026,AP,SAIC-VW,VW316-9-IP,Automation,250219,M,Equipment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tes</t>
+          <t>SAIC-VW</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
+          <t>Xia Yang_夏阳(uxiay057)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Li Yanchen_李彦辰(ulixy466)</t>
+          <t>Hao Xiuxia_郝秀霞(uhaox031)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zhou Meijiao01_周美娇(uzhom121)</t>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Phase 3 Gate Exit-FPR</t>
+          <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：100；
-Zhao Kailiang的PKR打分：100；
-</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Wang Hao23的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,style="color:
-Lu Dinghao,Submitted
-Xu Shirong,Submitted
-Zhao Kailiang,Submitted</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Gongchao.Lu@yanfeng.com; Hao.Wang23@yanfeng.com; Shirong.Xu@yanfeng.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>30034171-EBP</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>30034171-2026,AP,Jianghuai,JHC-sun visor,assy, 260074, NT,Equipment</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Jianghuai</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Wang Baowei_王保卫(uwanb363)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Chen Zhibin01_陈志斌(uchez368)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Phase 4 Manufacturing Development</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Phase 4 Gate Exit-CPA</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：100；
-Zhao Kailiang的PKR打分：100；
-</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Wang Hao23的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>本周</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,style="color:
-Lu Dinghao,Submitted
-Xu Shirong,Submitted
-Zhao Kailiang,Submitted</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>30034168-EBP</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>30034168-2026,AP,SVW,A-SUV-mirror,assembly,260008,15T,Equipment</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SVW</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Wang Baowei_王保卫(uwanb363)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Zhou Liwen_周理文(uzhol008)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Phase 4 Manufacturing Development</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Phase 4 Gate Exit-CPA</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：100；
 Wang Hao23的PKR打分：100；
@@ -797,17 +589,17 @@
 </t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>本周</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Total,Confirmed
 Wang Hao23,Confirmed
@@ -816,176 +608,186 @@
 Zhao Kailiang,Confirmed</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>完成确认</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Dinghao.Lu@yanfeng.com; Gongchao.Lu@yanfeng.com</t>
+        </is>
+      </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>30034480-EBP</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>30034480-2028,AP,Toyota,780B,Spraying,260086,T,Equipment</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Toyota</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Chen Ziyi01_陈子翌(uchez443)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>30028728-EBP</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30028728-2025,AP,smartmi,MX11-DAB,Lamination.250190,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>smartmi</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Guo Xinjie_郭新杰(uguox097)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Liu Cong02_刘聪(uliuc396)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Phase 4 Gate Exit-CPA</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2027-03-31</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
+Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
 Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；
+Xu Shirong的PKR打分：100；
 </t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Total,Submitted
-Wang Hao23,style="color:
+Wang Hao23,Submitted
 Lu Dinghao,Submitted
 Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>30034479-EBP</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>30034479-2027,AP,Toyota,780B,Spraying,260085,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Toyota</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Phase 2 Concept Definition</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Phase 3 Gate Exit-FPR</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>30030383-EBP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30030383-2027,AP,Mercedes-Benz,EU V530-CUN,Lamination,250275,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Fan Jiejie_樊皆杰(ufanj028)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Huang Dongfang01_黄东方(uhuad056)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2027-09-30</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：100；
 Wang Hao23的PKR打分：100；
@@ -995,17 +797,17 @@
 </t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Total,Confirmed
 Wang Hao23,Confirmed
@@ -1014,279 +816,178 @@
 Xu Shirong,Confirmed</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>完成确认</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>30034479-EBP</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>30034479-2027,AP,Toyota,780B,Spraying,260085,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Toyota</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Chen Jie04_陈洁(uchej018)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Phase 2 Concept Definition</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>30031042-EBP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30031042-2026,AP,XPENG,G02-Vent,EOL,250315,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>XPENG</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Wang Xiang02_王翔(uwanx029)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Zhou Liwen_周理文(uzhol008)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Post Launch</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；
-</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Wang Hao23的PKR打分：0；
-Lu Gongchao的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,style="color:
-Lu Dinghao,Submitted
-Lu Gongchao,style="color:
-Xu Shirong,style="color:</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>30034477-EBP</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>30034477-2025,AP,Toyota,780B-DP,Flaming, 260079,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Toyota</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Huang Linjian_黄琳健(uhual254)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Phase 3 Design Feasibility</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Phase 4 Gate Exit-CPA</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
-Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：0；
+Xu Shirong的PKR打分：100；
 Zhao Kailiang的PKR打分：100；
 </t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Wang Hao23的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>下周</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Total,Submitted
-Wang Hao23,style="color:
-Lu Dinghao,Submitted
-Xu Shirong,style="color:
-Zhao Kailiang,Submitted</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>未评分(工程师)</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Total,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Xu Shirong,Confirmed
+Zhao Kailiang,Confirmed</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>完成确认</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>30034746-EBP</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>30034746-2026,AP,Huawei Anhui,X90-DP,260115,glue spray,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>30031541-EBP</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>30031541-2026,AP,Huawei Anhui,EHV-DP,Lamination,250340,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Huawei Anhui</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Cheng Debao_程德宝(uched025)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Xia Yang_夏阳(uxiay057)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Xu Shirong_徐时荣(uxuxs004)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Phase 4 Manufacturing Development</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>2027-09-25</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Post Launch</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t xml:space="preserve">最低打分：100；
 Wang Hao23的PKR打分：100；
@@ -1296,17 +997,17 @@
 </t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>本周</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Total,Confirmed
 Wang Hao23,Confirmed
@@ -1315,6 +1016,308 @@
 Xu Shirong,Confirmed</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>完成确认</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>30030313-EBP</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30030313-2026,AP,Tes,Highland-FC,Assembly,250268,3T,Equipment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Tes</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Li Yanchen_李彦辰(ulixy466)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Zhou Meijiao01_周美娇(uzhom121)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Total,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Xu Shirong,Confirmed
+Zhao Kailiang,Confirmed</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>完成确认</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>30033409-EBP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30033409-2026,AP,Huawei Anhui,F05/F03 CNSL,Assembly,260037,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Huawei Anhui</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Feng Quanhua_冯全华(ufenq022)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Lu Dinghao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,style="color:
+Xu Shirong,Submitted
+Zhao Kailiang,Submitted</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>30034477-EBP</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>30034477-2025,AP,Toyota,780B-DP,Flaming, 260079,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Total,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Xu Shirong,Confirmed
+Zhao Kailiang,Confirmed</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>完成确认</t>
@@ -1325,22 +1328,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>30035162-EBP</t>
+          <t>30034479-EBP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>30035162-2026,AP,BJEV,X90,Lamination,260133,M,Equipment</t>
+          <t>30034479-2027,AP,Toyota,780B,Spraying,260085,M,Equipment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BJEV</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Shang Bing_尚兵(ushab007)</t>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1348,19 +1351,15 @@
           <t>Chen Jie04_陈洁(uchej018)</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1370,28 +1369,28 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2027-10-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Phase 3 Gate Exit-FPR</t>
+          <t>Phase 4 Gate Exit-CPA</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
 Lu Gongchao的PKR打分：100；
 Xu Shirong的PKR打分：100；
@@ -1400,7 +1399,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；</t>
+          <t>完成</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1410,16 +1409,16 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Total,Submitted
-Wang Hao23,style="color:
-Lu Dinghao,Submitted
-Lu Gongchao,Submitted
-Xu Shirong,Submitted</t>
+          <t>Total,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Lu Gongchao,Confirmed
+Xu Shirong,Confirmed</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>未评分(工程师)</t>
+          <t>完成确认</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -1427,62 +1426,58 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>30036184-EBP</t>
+          <t>30034479-EBP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30036184-2026,AP,JAC-VW,JHB-sunvisor,assem, 260180, 2T,Equipment</t>
+          <t>30034479-2027,AP,Toyota,780B,Spraying,260085,M,Equipment</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JAC-VW</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wang Baowei_王保卫(uwanb363)</t>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chen Zhibin01_陈志斌(uchez368)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1492,37 +1487,36 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
-Xu Shirong的PKR打分：0；
-Zhao Kailiang的PKR打分：100；
+Lu Gongchao的PKR打分：100；
+Xu Shirong的PKR打分：100；
 </t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Wang Hao23的PKR打分：0；
-Xu Shirong的PKR打分：0；</t>
+          <t>完成</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>下周</t>
+          <t>本周</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Total,Submitted
-Wang Hao23,style="color:
-Lu Dinghao,Submitted
-Xu Shirong,style="color:
-Zhao Kailiang,Submitted</t>
+          <t>Total,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Lu Gongchao,Confirmed
+Xu Shirong,Confirmed</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>未评分(工程师)</t>
+          <t>完成确认</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -1530,185 +1524,2314 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>30035707-EBP</t>
+          <t>30034480-EBP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>30035707-2026,AP,Brilliance-BMW,RGB 8PIN-light,assemble,260156,T,Equipment</t>
+          <t>30034480-2028,AP,Toyota,780B,Spraying,260086,T,Equipment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brilliance-BMW</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Chen Jiarong_陈佳荣(uchej731)</t>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhou Liwen_周理文(uzhol008)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Xu Shirong_徐时荣(uxuxs004)</t>
-        </is>
-      </c>
+          <t>Kan Chengben_阚城奔(ukanc012)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Total,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Lu Gongchao,Confirmed
+Xu Shirong,Confirmed</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>完成确认</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>30034480-EBP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>30034480-2028,AP,Toyota,780B,Spraying,260086,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Kan Chengben_阚城奔(ukanc012)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>Phase 3 Gate Exit-FPR</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最低打分：0；
-Wang Hao23的PKR打分：0；
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Total,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Lu Gongchao,Confirmed
+Xu Shirong,Confirmed</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>完成确认</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>30034478-EBP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>30034478-2026,AP,Toyota,780B-DP, flaming,260080,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Kan Chengben_阚城奔(ukanc012)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
 Lu Dinghao的PKR打分：100；
 Xu Shirong的PKR打分：100；
 Zhao Kailiang的PKR打分：100；
 </t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Wang Hao23的PKR打分：0；</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Total,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Xu Shirong,Confirmed
+Zhao Kailiang,Confirmed</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>完成确认</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>30034480-EBP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>30034480-2028,AP,Toyota,780B,Spraying,260086,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Kan Chengben_阚城奔(ukanc012)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>本周</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Total,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Lu Gongchao,Confirmed
+Xu Shirong,Confirmed</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>完成确认</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>30034615-EBP</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>30034615-2026,AP,BYD,MR&amp;ST-IP, Glue,260091, M,Equipment</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BYD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Yuan Shuai_袁帅(uyuas003)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Total,Submitted
-Wang Hao23,style="color:
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>30030761-EBP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>30030761-2025,AP,SAIC-VW,VW416-IP,Automatin,250306,M,,Equipment</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SAIC-VW</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Xia Yang_夏阳(uxiay057)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Liu Jinghua01_刘璟华(uliuj595)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
 Lu Dinghao,Submitted
 Xu Shirong,Submitted
 Zhao Kailiang,Submitted</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>未确认(Cao Liang)</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>30031304-EBP</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>30031304-2026,AP,Chery,EHV-Pilla,Welding,250319,1M,Equipment</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chery</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Xia Yang_夏阳(uxiay057)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Huang Sheng02_黄圣(uhuas068)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Total,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Xu Shirong,Confirmed
+Zhao Kailiang,Confirmed</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>完成确认</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>30031537-EBP</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>30031537-2026,AP,Huawei Anhui,EHV-DP,Lamination,250338,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Huawei Anhui</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Xia Yang_夏阳(uxiay057)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Post Launch</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Total,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Lu Gongchao,Confirmed
+Xu Shirong,Confirmed</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>完成确认</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>30033461-EBP</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>30033461-2026,AP,SVW,B-SUV-mirror,assy,260041,1M,Equipment</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SVW</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Lu Dinghao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,style="color:
+Xu Shirong,Submitted
+Zhao Kailiang,Submitted</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>未评分(工程师)</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>30031540-EBP</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>30031540-2026,AP,Huawei Anhui,EHV-DP,Lamination,250339,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Huawei Anhui</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Xia Yang_夏阳(uxiay057)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>30034624-EBP</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>30034624-2026,AP,BYD,Lamination,260102,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BYD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2027-09-30</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>30034747-EBP</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>30034747-2026,AP,Huawei Anhui,X90-DP,260116,Glue spray,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Huawei Anhui</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Cheng Debao_程德宝(uched025)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2027-09-30</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>30034166-EBP</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>30034166-2026,AP,SAIC-GM,C1UL-2,CNSL,Lamination,260073,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SAIC-GM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Fan Aiqiang01_樊爱强(ufana018)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>30035205-EBP</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>30035205-2027,AP,SERES Motors,E68-DP,lamination,260138,2M,Equipment</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SERES Motors</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Yuan Shuai_袁帅(uyuas003)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>30033043-EBP</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>30033043-2027,AP,General Motors,C1UL-IP,Lamination,260020,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>General Motors</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Guo Zhengyang_郭正阳(uguoz023)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Gao Yiheng01_高一恒(ugaoy160)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>30035208-EBP</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>30035208-2026,AP,Jianghuai,C673-DP,Foam Sticking,260140,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Jianghuai</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2027-10-29</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Lu Dinghao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,style="color:
+Xu Shirong,Submitted
+Zhao Kailiang,Submitted</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>30035161-EBP</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>30035161-2026,AP,BJEV,X90,Lamination,260132,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BJEV</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2027-10-20</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,style="color:
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>30035162-EBP</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>30035162-2026,AP,BJEV,X90,Lamination,260133,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BJEV</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2027-10-20</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,style="color:
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>30035945-EBP</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>30035945-2027,NA,Toyota,815/825D-OHC, assy, 260168, 2M,Equipment</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Wei Shaoguan_韦少官(uweis086)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2027-10-31</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,Submitted
+Xu Shirong,Submitted
+Zhao Kailiang,Submitted</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>未确认(Cao Liang)</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>30033911-EBP</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>30033911-2026,NA,Stellantis,WL-DP,laminnation,260060,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Wang Xiang02_王翔(uwanx029)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Jin Yulong01_金宇隆(ujiny132)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：100；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：100；
+Lu Gongchao的PKR打分：100；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Total,Confirmed
+Wang Hao23,Confirmed
+Lu Dinghao,Confirmed
+Lu Gongchao,Confirmed
+Xu Shirong,Confirmed</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>完成确认</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>30036039-EBP</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>30036039-2026,AP,SERES Motors,L97-DAB, Lamination, 260171, 1T,Equipment</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SERES Motors</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Huang Dongfang01_黄东方(uhuad056)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phase 3 Design Feasibility</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Lu Dinghao的PKR打分：0；
+Lu Gongchao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,style="color:
+Lu Gongchao,style="color:
+Xu Shirong,Submitted</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>30035707-EBP</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>30035707-2026,AP,Brilliance-BMW,RGB 8PIN-light,assemble,260156,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Brilliance-BMW</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Chen Jiarong_陈佳荣(uchej731)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Zhou Liwen_周理文(uzhol008)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Xu Shirong_徐时荣(uxuxs004)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最低打分：0；
+Wang Hao23的PKR打分：100；
+Lu Dinghao的PKR打分：0；
+Xu Shirong的PKR打分：100；
+Zhao Kailiang的PKR打分：100；
+</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Lu Dinghao的PKR打分：0；</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Total,Submitted
+Wang Hao23,Submitted
+Lu Dinghao,style="color:
+Xu Shirong,Submitted
+Zhao Kailiang,Submitted</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>未评分(工程师)</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>30036085-EBP</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>30036085-2026,AP,SERES Motors,L97-light，assemble,260173,T,Equipment</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>SERES Motors</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Chen Jiarong_陈佳荣(uchej731)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Huang Sheng02_黄圣(uhuas068)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Xu Shirong_徐时荣(uxuxs004)</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Phase 1 Quotation</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>2026-11-20</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Phase 1 Gate Exit-GO</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
         <is>
           <t>phase1不适用</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>下周</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>本周</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
